--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -150,9 +150,6 @@
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -478,9 +475,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11">
-      <c r="C11" s="6"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Material</t>
   </si>
@@ -22,6 +22,12 @@
     <t>Color</t>
   </si>
   <si>
+    <t>substrate</t>
+  </si>
+  <si>
+    <t>grey</t>
+  </si>
+  <si>
     <t>t_SiO2</t>
   </si>
   <si>
@@ -73,7 +79,7 @@
     <t>t_Au</t>
   </si>
   <si>
-    <t>grey</t>
+    <t>violet red</t>
   </si>
 </sst>
 </file>
@@ -133,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -141,6 +147,15 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -381,98 +396,109 @@
         <v>3</v>
       </c>
       <c r="B2" s="4">
-        <v>300.0</v>
+        <v>400000.0</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="4">
-        <v>300.0</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Material</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>t_Au</t>
-  </si>
-  <si>
-    <t>violet red</t>
   </si>
 </sst>
 </file>
@@ -498,7 +495,7 @@
         <v>300.0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+  <si>
+    <t>Layer</t>
+  </si>
   <si>
     <t>Material</t>
   </si>
@@ -19,10 +22,19 @@
     <t>Thickness</t>
   </si>
   <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Indent</t>
+  </si>
+  <si>
     <t>Color</t>
   </si>
   <si>
     <t>substrate</t>
+  </si>
+  <si>
+    <t>nm</t>
   </si>
   <si>
     <t>grey</t>
@@ -136,30 +148,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -376,6 +370,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="6.13"/>
+    <col customWidth="1" min="4" max="4" width="7.5"/>
+    <col customWidth="1" min="5" max="5" width="7.63"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -384,118 +383,217 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="A2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
         <v>400000.0</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>6</v>
+      <c r="A3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>8</v>
+      <c r="A4" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>10</v>
+      <c r="A5" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8000.0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="A6" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5000.0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5000.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5000.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3000.0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>8000.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2">
+        <v>8000.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -114,7 +114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,6 +125,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
         <bgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -156,6 +162,9 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -400,7 +409,7 @@
       <c r="A2" s="2">
         <v>0.0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2">

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -589,7 +589,7 @@
       <c r="A11" s="2">
         <v>9.0</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="2">

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -114,7 +114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,6 +131,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -165,6 +171,9 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -413,7 +422,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>400000.0</v>
+        <v>400.0</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -589,7 +598,7 @@
       <c r="A11" s="2">
         <v>9.0</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="2">

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -88,7 +88,7 @@
     <t>pink</t>
   </si>
   <si>
-    <t>t_Au</t>
+    <t>this_is_a_long_ass_material</t>
   </si>
 </sst>
 </file>
@@ -390,6 +390,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="6.13"/>
+    <col customWidth="1" min="2" max="2" width="21.5"/>
     <col customWidth="1" min="4" max="4" width="7.5"/>
     <col customWidth="1" min="5" max="5" width="7.63"/>
   </cols>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>Layer</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>pink</t>
-  </si>
-  <si>
-    <t>this_is_a_long_ass_material</t>
   </si>
 </sst>
 </file>
@@ -423,7 +420,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>400.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -596,24 +593,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2">
-        <v>300.0</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2">
-        <v>8000.0</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>Layer</t>
   </si>
@@ -86,6 +86,15 @@
   </si>
   <si>
     <t>pink</t>
+  </si>
+  <si>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t>lightblue</t>
+  </si>
+  <si>
+    <t>Test2</t>
   </si>
 </sst>
 </file>
@@ -157,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -172,6 +181,9 @@
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,12 +605,44 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>500.0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2">
+        <v>9000.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="5">
+        <v>69.0</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>Layer</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>lightblue</t>
-  </si>
-  <si>
-    <t>Test2</t>
   </si>
 </sst>
 </file>
@@ -135,14 +132,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -166,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -181,9 +178,6 @@
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,7 +522,7 @@
       <c r="A7" s="2">
         <v>5.0</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="2">
@@ -608,7 +602,7 @@
       <c r="A11" s="2">
         <v>9.0</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="2">
@@ -622,26 +616,6 @@
       </c>
       <c r="F11" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="5">
-        <v>69.0</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Layer</t>
   </si>
@@ -49,7 +49,7 @@
     <t>t_Ti</t>
   </si>
   <si>
-    <t>red</t>
+    <t>gold</t>
   </si>
   <si>
     <t>t_TiO2</t>
@@ -61,7 +61,7 @@
     <t>t_Pt</t>
   </si>
   <si>
-    <t>yellow</t>
+    <t>lightblue</t>
   </si>
   <si>
     <t>t_LNO</t>
@@ -79,19 +79,13 @@
     <t>t_NiCr</t>
   </si>
   <si>
-    <t>gold</t>
-  </si>
-  <si>
     <t>t_TiW</t>
   </si>
   <si>
-    <t>pink</t>
-  </si>
-  <si>
     <t>Test1</t>
   </si>
   <si>
-    <t>lightblue</t>
+    <t>Test2</t>
   </si>
 </sst>
 </file>
@@ -426,7 +420,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>1000.0</v>
+        <v>400000.0</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -452,7 +446,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -466,13 +460,13 @@
         <v>11</v>
       </c>
       <c r="C4" s="2">
-        <v>300.0</v>
+        <v>245.0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0</v>
+        <v>245.0</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
@@ -492,7 +486,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="2">
-        <v>8000.0</v>
+        <v>300.0</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
@@ -506,13 +500,13 @@
         <v>15</v>
       </c>
       <c r="C6" s="2">
-        <v>300.0</v>
+        <v>876.0</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="2">
-        <v>5000.0</v>
+        <v>876.0</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -532,7 +526,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="2">
-        <v>5000.0</v>
+        <v>300.0</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -546,13 +540,13 @@
         <v>19</v>
       </c>
       <c r="C8" s="2">
-        <v>300.0</v>
+        <v>278.0</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="2">
-        <v>5000.0</v>
+        <v>278.0</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>20</v>
@@ -572,10 +566,10 @@
         <v>7</v>
       </c>
       <c r="E9" s="2">
-        <v>3000.0</v>
+        <v>300.0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -583,19 +577,19 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2">
-        <v>300.0</v>
+        <v>349.0</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="2">
-        <v>8000.0</v>
+        <v>349.0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -603,19 +597,39 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2">
-        <v>500.0</v>
+        <v>600.0</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="2">
-        <v>9000.0</v>
+        <v>600.0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2">
+        <v>123.0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2">
+        <v>123.0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -440,13 +440,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>300.0</v>
+        <v>3000.0</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="2">
-        <v>300.0</v>
+        <v>500.0</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -460,13 +460,13 @@
         <v>11</v>
       </c>
       <c r="C4" s="2">
-        <v>245.0</v>
+        <v>5000.0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="2">
-        <v>245.0</v>
+        <v>100.0</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
@@ -480,13 +480,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>300.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2">
-        <v>300.0</v>
+        <v>500.0</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
@@ -500,13 +500,13 @@
         <v>15</v>
       </c>
       <c r="C6" s="2">
-        <v>876.0</v>
+        <v>4500.0</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="2">
-        <v>876.0</v>
+        <v>3000.0</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -526,7 +526,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="2">
-        <v>300.0</v>
+        <v>500.0</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -540,13 +540,13 @@
         <v>19</v>
       </c>
       <c r="C8" s="2">
-        <v>278.0</v>
+        <v>1500.0</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="2">
-        <v>278.0</v>
+        <v>500.0</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>20</v>
@@ -560,13 +560,13 @@
         <v>21</v>
       </c>
       <c r="C9" s="2">
-        <v>300.0</v>
+        <v>3000.0</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="2">
-        <v>300.0</v>
+        <v>500.0</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>12</v>
@@ -580,13 +580,13 @@
         <v>22</v>
       </c>
       <c r="C10" s="2">
-        <v>349.0</v>
+        <v>5000.0</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="2">
-        <v>349.0</v>
+        <v>500.0</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>10</v>
@@ -600,13 +600,13 @@
         <v>23</v>
       </c>
       <c r="C11" s="2">
-        <v>600.0</v>
+        <v>3456.0</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="2">
-        <v>600.0</v>
+        <v>5000.0</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>16</v>
@@ -620,13 +620,13 @@
         <v>24</v>
       </c>
       <c r="C12" s="2">
-        <v>123.0</v>
+        <v>45.0</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="2">
-        <v>123.0</v>
+        <v>500.0</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>10</v>
